--- a/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8937810251186573</v>
+        <v>0.9985448682732995</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7900528276994305</v>
+        <v>1.686821935045501</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1037281974192268</v>
+        <v>0.6882770667722015</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1292736108894</v>
+        <v>40.80318452543929</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8330848013472778</v>
+        <v>0.2232740433031848</v>
       </c>
       <c r="C3" t="n">
-        <v>0.686074165927846</v>
+        <v>1.798864739704409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1470106354194318</v>
+        <v>1.575590696401224</v>
       </c>
       <c r="E3" t="n">
-        <v>21.42780514415884</v>
+        <v>87.58805826946869</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3363668202095515</v>
+        <v>0.0608166708235236</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1215380638045284</v>
+        <v>0.2134515799796908</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2148287564050231</v>
+        <v>0.1526349091561672</v>
       </c>
       <c r="E4" t="n">
-        <v>176.7584159893608</v>
+        <v>71.50797814225123</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1134615004325696</v>
+        <v>0.1117867776625432</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2839703813026161</v>
+        <v>0.005394216754002645</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1705088808700465</v>
+        <v>0.1063925609085406</v>
       </c>
       <c r="E5" t="n">
-        <v>60.04460045723638</v>
+        <v>1972.344934593046</v>
       </c>
     </row>
     <row r="6">
@@ -538,149 +538,111 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3146655282682057</v>
+        <v>0.1653942399903137</v>
       </c>
       <c r="C6" t="n">
-        <v>0.317617585405287</v>
+        <v>0.9920941427715224</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002952057137081299</v>
+        <v>0.8266999027812088</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9294375603650563</v>
+        <v>83.32877568168411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kappa_p1</t>
+          <t>lambda1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6794655592954768</v>
+        <v>0.1149302912364081</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4460670206811996</v>
+        <v>0.2841873264001693</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2333985386142772</v>
+        <v>0.1692570351637612</v>
       </c>
       <c r="E7" t="n">
-        <v>52.3236481948046</v>
+        <v>59.55826296258805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kappa_p2</t>
+          <t>lambda2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8540928948348463</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5069238948386092</v>
+        <v>0.1465827690962086</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3471689999962371</v>
+        <v>0.1465827690962086</v>
       </c>
       <c r="E8" t="n">
-        <v>68.48542819366726</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>theta_p1</t>
+          <t>sigma1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2674037039641027</v>
+        <v>0.1309112039372257</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2170303455377147</v>
+        <v>0.07893329841780578</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05037335842638802</v>
+        <v>0.05197790551941994</v>
       </c>
       <c r="E9" t="n">
-        <v>23.21028347514395</v>
+        <v>65.85041618847993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>theta_p2</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.199384214240212</v>
+        <v>0.2202902139587959</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2060174641659934</v>
+        <v>0.1029802960104409</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006633249925781404</v>
+        <v>0.1173099179483551</v>
       </c>
       <c r="E10" t="n">
-        <v>3.219751273337113</v>
+        <v>113.9149162442312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sigma1</t>
+          <t>sigma_err</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5980758568817767</v>
+        <v>9.350837272865996e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6182332454250331</v>
+        <v>9.119690747063867e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02015738854325644</v>
+        <v>2.31146525802129e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>3.260482785813032</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sigma2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.2092232280753855</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.5832233325435531</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.3740001044681676</v>
-      </c>
-      <c r="E12" t="n">
-        <v>64.12639611606049</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sigma_err</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.001355130359821988</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.00131702604971008</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.810431011190747e-05</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.893208537545286</v>
+        <v>2.534587325524693</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,187 +462,437 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9985448682732995</v>
+        <v>0.4551530266699514</v>
       </c>
       <c r="C2" t="n">
-        <v>1.686821935045501</v>
+        <v>0.4667789959088117</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6882770667722015</v>
+        <v>0.01162596923886022</v>
       </c>
       <c r="E2" t="n">
-        <v>40.80318452543929</v>
+        <v>2.490679602286867</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kappa2</t>
+          <t xml:space="preserve">  ↳ SE(kappa1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2232740433031848</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.798864739704409</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.575590696401224</v>
-      </c>
-      <c r="E3" t="n">
-        <v>87.58805826946869</v>
+        <v>9.278429230668732e-09</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>theta1</t>
+          <t>kappa2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0608166708235236</v>
+        <v>0.5227926005801151</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2134515799796908</v>
+        <v>0.5217542397050881</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1526349091561672</v>
+        <v>0.001038360875027067</v>
       </c>
       <c r="E4" t="n">
-        <v>71.50797814225123</v>
+        <v>0.1990134043978217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>theta2</t>
+          <t xml:space="preserve">  ↳ SE(kappa2)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1117867776625432</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.005394216754002645</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.1063925609085406</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1972.344934593046</v>
+        <v>3.064104467880361e-06</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gamma1</t>
+          <t>theta1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1653942399903137</v>
+        <v>0.1254936182515281</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9920941427715224</v>
+        <v>0.114264358772</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8266999027812088</v>
+        <v>0.01122925947952808</v>
       </c>
       <c r="E6" t="n">
-        <v>83.32877568168411</v>
+        <v>9.827438407049247</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lambda1</t>
+          <t xml:space="preserve">  ↳ SE(theta1)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1149302912364081</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2841873264001693</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1692570351637612</v>
-      </c>
-      <c r="E7" t="n">
-        <v>59.55826296258805</v>
+        <v>1.155096400270214e-07</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lambda2</t>
+          <t>theta2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.1337057261661776</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1465827690962086</v>
+        <v>0.1139588215811123</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1465827690962086</v>
+        <v>0.01974690458506534</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>17.32810528495165</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sigma1</t>
+          <t xml:space="preserve">  ↳ SE(theta2)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1309112039372257</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.07893329841780578</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.05197790551941994</v>
-      </c>
-      <c r="E9" t="n">
-        <v>65.85041618847993</v>
+        <v>2.246539967276284e-06</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t>gamma1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2202902139587959</v>
+        <v>0.04165765125494403</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1029802960104409</v>
+        <v>0.05525232825719199</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1173099179483551</v>
+        <v>0.01359467700224797</v>
       </c>
       <c r="E10" t="n">
-        <v>113.9149162442312</v>
+        <v>24.60471337780847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ↳ SE(gamma1)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.299648425341672e-07</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lambda1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.1041481803181856</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.3287316348024272</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2245834544842416</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-68.31817528581321</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(lambda1)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.991497152733666e-08</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lambda2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1997465419729818</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1645174579513944</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.03522908402158736</v>
+      </c>
+      <c r="E14" t="n">
+        <v>21.41358398085361</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(lambda2)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7.950277344289922e-06</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sigma1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3074353584533804</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2266588351604691</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0807765232929113</v>
+      </c>
+      <c r="E16" t="n">
+        <v>35.63793277051099</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma1)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.410890487278283e-05</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sigma2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.1379414429329338</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.08105774583748999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.05688369709544376</v>
+      </c>
+      <c r="E18" t="n">
+        <v>70.17675671550009</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma2)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.421132343928594e-05</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>sigma_err</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>9.350837272865996e-05</v>
-      </c>
-      <c r="C11" t="n">
-        <v>9.119690747063867e-05</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.31146525802129e-06</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.534587325524693</v>
+      <c r="B20" t="n">
+        <v>2.944925022162377e-05</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.692778853313162e-05</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.52146168849215e-06</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9.363790440458096</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma_err)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.005621709577324699</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4551530266699514</v>
+        <v>1.458330966823688</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4667789959088117</v>
+        <v>1.497869415359124</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01162596923886022</v>
+        <v>0.03953844853543598</v>
       </c>
       <c r="E2" t="n">
-        <v>2.490679602286867</v>
+        <v>2.639645895029934</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.278429230668732e-09</v>
+        <v>5.500179028887136e-05</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5227926005801151</v>
+        <v>0.9888598710576902</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5217542397050881</v>
+        <v>0.8403708700586656</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001038360875027067</v>
+        <v>0.1484890009990246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1990134043978217</v>
+        <v>17.66946074518965</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.064104467880361e-06</v>
+        <v>1.047660959318493e-05</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,16 +550,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1254936182515281</v>
+        <v>0.3502099831403332</v>
       </c>
       <c r="C6" t="n">
-        <v>0.114264358772</v>
+        <v>0.5171377746803077</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01122925947952808</v>
+        <v>0.1669277915399745</v>
       </c>
       <c r="E6" t="n">
-        <v>9.827438407049247</v>
+        <v>32.27917195628738</v>
       </c>
     </row>
     <row r="7">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.155096400270214e-07</v>
+        <v>0.6252149313879698</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,16 +594,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1337057261661776</v>
+        <v>0.1463400389961272</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1139588215811123</v>
+        <v>0.1362189365177941</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01974690458506534</v>
+        <v>0.01012110247833312</v>
       </c>
       <c r="E8" t="n">
-        <v>17.32810528495165</v>
+        <v>7.430026057361717</v>
       </c>
     </row>
     <row r="9">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.246539967276284e-06</v>
+        <v>0.1454657965030183</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04165765125494403</v>
+        <v>0.00974787025612381</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05525232825719199</v>
+        <v>0.007091249898136207</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01359467700224797</v>
+        <v>0.002656620357987603</v>
       </c>
       <c r="E10" t="n">
-        <v>24.60471337780847</v>
+        <v>37.46335830987768</v>
       </c>
     </row>
     <row r="11">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.299648425341672e-07</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,17 +682,15 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1041481803181856</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3287316348024272</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2245834544842416</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-68.31817528581321</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -701,7 +699,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.991497152733666e-08</v>
+        <v>0.1502906157840412</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,17 +724,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1997465419729818</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1645174579513944</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03522908402158736</v>
-      </c>
-      <c r="E14" t="n">
-        <v>21.41358398085361</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -745,7 +741,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.950277344289922e-06</v>
+        <v>0.02155017547981297</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,16 +766,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3074353584533804</v>
+        <v>0.5866423594833005</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2266588351604691</v>
+        <v>0.6212639472228774</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0807765232929113</v>
+        <v>0.03462158773957691</v>
       </c>
       <c r="E16" t="n">
-        <v>35.63793277051099</v>
+        <v>5.572766276610684</v>
       </c>
     </row>
     <row r="17">
@@ -789,7 +785,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.410890487278283e-05</v>
+        <v>0.04656106875516445</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,16 +810,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1379414429329338</v>
+        <v>0.393669592364055</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08105774583748999</v>
+        <v>0.4715349666650857</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05688369709544376</v>
+        <v>0.07786537430103069</v>
       </c>
       <c r="E18" t="n">
-        <v>70.17675671550009</v>
+        <v>16.51317077325798</v>
       </c>
     </row>
     <row r="19">
@@ -833,7 +829,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.421132343928594e-05</v>
+        <v>0.04887550269223144</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,16 +854,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.944925022162377e-05</v>
+        <v>4.82343532758325e-05</v>
       </c>
       <c r="C20" t="n">
-        <v>2.692778853313162e-05</v>
+        <v>4.775308408511788e-05</v>
       </c>
       <c r="D20" t="n">
-        <v>2.52146168849215e-06</v>
+        <v>4.812691907146114e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>9.363790440458096</v>
+        <v>1.007828499321152</v>
       </c>
     </row>
     <row r="21">
@@ -877,7 +873,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.005621709577324699</v>
+        <v>7.44649304401312e-07</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LogLike</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Filipovic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Abs Error, Kalman</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Rel Error (%), Kalman</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Abs Error, Filipovic</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rel Error (%), Filipovic</t>
         </is>
       </c>
     </row>
@@ -462,433 +487,337 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.458330966823688</v>
+        <v>0.7554044148993988</v>
       </c>
       <c r="C2" t="n">
-        <v>1.497869415359124</v>
+        <v>0.6222280301312973</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03953844853543598</v>
+        <v>7565.256876022064</v>
       </c>
       <c r="E2" t="n">
-        <v>2.639645895029934</v>
+        <v>0.6487163195834194</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7490602403257222</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.006344174573676642</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8469511839151861</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1003439207423028</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.39597476147835</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(kappa1)</t>
+          <t>kappa2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.500179028887136e-05</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5716029704835149</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2086341955519944</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6433517546680012</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5882238779386133</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01662090745509837</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.825609105387747</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0551278767293879</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.371920929592221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kappa2</t>
+          <t>theta1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9888598710576902</v>
+        <v>0.2304795048187174</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8403708700586656</v>
+        <v>4.053659780325556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1484890009990246</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>17.66946074518965</v>
+        <v>0.2188528234975268</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3114920179524447</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.08101251313372732</v>
+      </c>
+      <c r="H4" t="n">
+        <v>26.00789377084309</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09263919445491792</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.74047138153668</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(kappa2)</t>
+          <t>theta2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.047660959318493e-05</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1704178218453681</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4588458707512628</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1883018934643933</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.09382414493231982</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07659367691304826</v>
+      </c>
+      <c r="H5" t="n">
+        <v>81.63535832732525</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09447774853207348</v>
+      </c>
+      <c r="J5" t="n">
+        <v>100.696626225824</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>theta1</t>
+          <t>gamma1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3502099831403332</v>
+        <v>0.1152397524093587</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5171377746803077</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1669277915399745</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>32.27917195628738</v>
+        <v>0.1094264117487634</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1557460089762224</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.04050625656686366</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26.00789377084309</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04631959722745896</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.74047138153668</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(theta1)</t>
+          <t>lambda1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6252149313879698</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.8704318175537991</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.554150388463109</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2940285356497346</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5764032819040644</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-196.0365107523824</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2940285356497346</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>theta2</t>
+          <t>lambda2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1463400389961272</v>
+        <v>0.3461378578233623</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1362189365177941</v>
+        <v>0.3058089548273573</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01012110247833312</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>7.430026057361717</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3572802058654481</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0111423480420858</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.118658089410645</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3572802058654481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(theta2)</t>
+          <t>sigma1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1454657965030183</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.4188131543039738</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01044369123911474</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3559335309243263</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06287962337964748</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17.66611401189288</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3559335309243263</v>
+      </c>
+      <c r="J9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gamma1</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00974787025612381</v>
+        <v>0.1518738330358538</v>
       </c>
       <c r="C10" t="n">
-        <v>0.007091249898136207</v>
+        <v>0.008704772850982043</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002656620357987603</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>37.46335830987768</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.09443994288255431</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05743389015329953</v>
+      </c>
+      <c r="H10" t="n">
+        <v>60.81525295364105</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.09443994288255431</v>
+      </c>
+      <c r="J10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(gamma1)</t>
+          <t>sigma_err</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>lambda1</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(lambda1)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.1502906157840412</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>lambda2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(lambda2)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.02155017547981297</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>sigma1</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5866423594833005</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.6212639472228774</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.03462158773957691</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5.572766276610684</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma1)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.04656106875516445</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>sigma2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.393669592364055</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.4715349666650857</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.07786537430103069</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.51317077325798</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma2)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.04887550269223144</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sigma_err</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4.82343532758325e-05</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.775308408511788e-05</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.812691907146114e-07</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.007828499321152</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma_err)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>7.44649304401312e-07</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.713119851236345e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.979876098342014e-07</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.828753606203103e-05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.15633754966758e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.693336172822498</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6.828753606203103e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7554044148993988</v>
+        <v>0.4499459489672587</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6222280301312973</v>
+        <v>0.06468716985833992</v>
       </c>
       <c r="D2" t="n">
-        <v>7565.256876022064</v>
+        <v>38688.94176053617</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6487163195834194</v>
+        <v>0.4548836816777024</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7490602403257222</v>
+        <v>0.4548840732360043</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006344174573676642</v>
+        <v>0.00493812426874557</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8469511839151861</v>
+        <v>1.085578625256365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1003439207423028</v>
+        <v>3.9155830183768e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>13.39597476147835</v>
+        <v>8.607870111876408e-05</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5716029704835149</v>
+        <v>1.037589282895192</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2086341955519944</v>
+        <v>0.01759516782815135</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6433517546680012</v>
+        <v>0.9288554871525836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5882238779386133</v>
+        <v>0.9288508912314156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01662090745509837</v>
+        <v>0.1087383916637762</v>
       </c>
       <c r="H3" t="n">
-        <v>2.825609105387747</v>
+        <v>11.70676506749294</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0551278767293879</v>
+        <v>4.595921167971362e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.371920929592221</v>
+        <v>0.0004947964427184175</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2304795048187174</v>
+        <v>0.1419711964130985</v>
       </c>
       <c r="C4" t="n">
-        <v>4.053659780325556</v>
+        <v>0.294339636426685</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2188528234975268</v>
+        <v>0.273596999430357</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3114920179524447</v>
+        <v>0.3765051155279259</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08101251313372732</v>
+        <v>0.2345339191148275</v>
       </c>
       <c r="H4" t="n">
-        <v>26.00789377084309</v>
+        <v>62.29235923819254</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09263919445491792</v>
+        <v>0.1029081160975689</v>
       </c>
       <c r="J4" t="n">
-        <v>29.74047138153668</v>
+        <v>27.33246159305799</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1704178218453681</v>
+        <v>0.4518312468210556</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4588458707512628</v>
+        <v>0.1017993524053032</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1883018934643933</v>
+        <v>0.2321685718121865</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09382414493231982</v>
+        <v>0.1687110271291187</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07659367691304826</v>
+        <v>0.2831202196919369</v>
       </c>
       <c r="H5" t="n">
-        <v>81.63535832732525</v>
+        <v>167.8137016350793</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09447774853207348</v>
+        <v>0.06345754468306777</v>
       </c>
       <c r="J5" t="n">
-        <v>100.696626225824</v>
+        <v>37.61315769508187</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1152397524093587</v>
+        <v>0.2249729744836294</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -632,22 +632,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1094264117487634</v>
+        <v>0.2274418408388512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1557460089762224</v>
+        <v>0.2274420366180021</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04050625656686366</v>
+        <v>0.002469062134372785</v>
       </c>
       <c r="H6" t="n">
-        <v>26.00789377084309</v>
+        <v>1.085578625256365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04631959722745896</v>
+        <v>1.9577915091884e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>29.74047138153668</v>
+        <v>8.607870111876408e-05</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.8704318175537991</v>
+        <v>-0.9933881919688475</v>
       </c>
       <c r="C7" t="n">
-        <v>0.554150388463109</v>
+        <v>0.02892491237276064</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -669,16 +669,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2940285356497346</v>
+        <v>-0.777551884717775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5764032819040644</v>
+        <v>0.2158363072510725</v>
       </c>
       <c r="H7" t="n">
-        <v>-196.0365107523824</v>
+        <v>-27.75844435505596</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2940285356497346</v>
+        <v>0.777551884717775</v>
       </c>
       <c r="J7" t="n">
         <v>-100</v>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3461378578233623</v>
+        <v>-0.6940503567669097</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3058089548273573</v>
+        <v>0.02640828509849624</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -703,19 +703,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3572802058654481</v>
+        <v>-0.5574984500978069</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0111423480420858</v>
+        <v>0.1365519066691029</v>
       </c>
       <c r="H8" t="n">
-        <v>3.118658089410645</v>
+        <v>-24.49368364076104</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3572802058654481</v>
+        <v>0.5574984500978069</v>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="9">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4188131543039738</v>
+        <v>0.2851933196914556</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01044369123911474</v>
+        <v>0.007415297726222798</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -737,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3559335309243263</v>
+        <v>0.3053682683518907</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06287962337964748</v>
+        <v>0.02017494866043512</v>
       </c>
       <c r="H9" t="n">
-        <v>17.66611401189288</v>
+        <v>6.606760017771901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3559335309243263</v>
+        <v>0.3053682683518907</v>
       </c>
       <c r="J9" t="n">
         <v>100</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1518738330358538</v>
+        <v>0.08578757489559263</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008704772850982043</v>
+        <v>0.008749832414587756</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -771,16 +771,16 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09443994288255431</v>
+        <v>0.037330638253033</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05743389015329953</v>
+        <v>0.04845693664255963</v>
       </c>
       <c r="H10" t="n">
-        <v>60.81525295364105</v>
+        <v>129.8047365654742</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09443994288255431</v>
+        <v>0.037330638253033</v>
       </c>
       <c r="J10" t="n">
         <v>100</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.713119851236345e-05</v>
+        <v>8.447315604758241e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>7.979876098342014e-07</v>
+        <v>9.482588146495875e-07</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6.828753606203103e-05</v>
+        <v>8.289751980873394e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.15633754966758e-06</v>
+        <v>1.575636238848469e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.693336172822498</v>
+        <v>1.90070371524247</v>
       </c>
       <c r="I11" t="n">
-        <v>6.828753606203103e-05</v>
+        <v>8.289751980873394e-05</v>
       </c>
       <c r="J11" t="n">
         <v>100</v>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim2.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4499459489672587</v>
+        <v>0.498335311302568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06468716985833992</v>
+        <v>0.1551522333099787</v>
       </c>
       <c r="D2" t="n">
-        <v>38688.94176053617</v>
+        <v>38620.77300299853</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4548836816777024</v>
+        <v>0.4546113019049752</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4548840732360043</v>
+        <v>0.454611378925467</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00493812426874557</v>
+        <v>0.04372393237710104</v>
       </c>
       <c r="H2" t="n">
-        <v>1.085578625256365</v>
+        <v>9.617870208275082</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9155830183768e-07</v>
+        <v>7.702049176216974e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.607870111876408e-05</v>
+        <v>1.694205102041609e-05</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.037589282895192</v>
+        <v>0.6462829974742926</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01759516782815135</v>
+        <v>0.01600788744929037</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9288554871525836</v>
+        <v>0.9288429747077483</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9288508912314156</v>
+        <v>0.9288383342725333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1087383916637762</v>
+        <v>0.2825553367982406</v>
       </c>
       <c r="H3" t="n">
-        <v>11.70676506749294</v>
+        <v>30.42029235577773</v>
       </c>
       <c r="I3" t="n">
-        <v>4.595921167971362e-06</v>
+        <v>4.640435215086391e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004947964427184175</v>
+        <v>0.0004995955748015917</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1419711964130985</v>
+        <v>0.1665711858906673</v>
       </c>
       <c r="C4" t="n">
-        <v>0.294339636426685</v>
+        <v>0.9036013124783661</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.273596999430357</v>
+        <v>0.1086332570187577</v>
       </c>
       <c r="F4" t="n">
         <v>0.3765051155279259</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2345339191148275</v>
+        <v>0.2099339296372586</v>
       </c>
       <c r="H4" t="n">
-        <v>62.29235923819254</v>
+        <v>55.75858626592485</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1029081160975689</v>
+        <v>0.2678718585091682</v>
       </c>
       <c r="J4" t="n">
-        <v>27.33246159305799</v>
+        <v>71.14693730882384</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4518312468210556</v>
+        <v>0.3470710462481773</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1017993524053032</v>
+        <v>0.09560340172538474</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2321685718121865</v>
+        <v>0.5848362318296356</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1687110271291187</v>
+        <v>0.1687430837946758</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2831202196919369</v>
+        <v>0.1783279624535015</v>
       </c>
       <c r="H5" t="n">
-        <v>167.8137016350793</v>
+        <v>105.6801608950613</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06345754468306777</v>
+        <v>0.4160931480349598</v>
       </c>
       <c r="J5" t="n">
-        <v>37.61315769508187</v>
+        <v>246.583823572441</v>
       </c>
     </row>
     <row r="6">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2249729744836294</v>
+        <v>0.249167655651284</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -632,22 +632,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2274418408388512</v>
+        <v>0.2273056509524876</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2274420366180021</v>
+        <v>0.2273056894627335</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002469062134372785</v>
+        <v>0.02186196618855052</v>
       </c>
       <c r="H6" t="n">
-        <v>1.085578625256365</v>
+        <v>9.617870208275082</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9577915091884e-07</v>
+        <v>3.851024588108487e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.607870111876408e-05</v>
+        <v>1.694205102041609e-05</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.9933881919688475</v>
+        <v>-0.5190624991331836</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02892491237276064</v>
+        <v>0.1486513271522864</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -669,16 +669,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.777551884717775</v>
+        <v>-0.4618055976220965</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2158363072510725</v>
+        <v>0.05725690151108709</v>
       </c>
       <c r="H7" t="n">
-        <v>-27.75844435505596</v>
+        <v>-12.39848581435806</v>
       </c>
       <c r="I7" t="n">
-        <v>0.777551884717775</v>
+        <v>0.4618055976220965</v>
       </c>
       <c r="J7" t="n">
         <v>-100</v>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.6940503567669097</v>
+        <v>-0.2976594368111677</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02640828509849624</v>
+        <v>0.03533556086207476</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -703,16 +703,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5574984500978069</v>
+        <v>-0.272056560302384</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1365519066691029</v>
+        <v>0.02560287650878379</v>
       </c>
       <c r="H8" t="n">
-        <v>-24.49368364076104</v>
+        <v>-9.41086532900616</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5574984500978069</v>
+        <v>0.272056560302384</v>
       </c>
       <c r="J8" t="n">
         <v>-100</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2851933196914556</v>
+        <v>0.3017185183495885</v>
       </c>
       <c r="C9" t="n">
-        <v>0.007415297726222798</v>
+        <v>0.00736355174699689</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -737,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3053682683518907</v>
+        <v>0.3052767234088358</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02017494866043512</v>
+        <v>0.003558205059247255</v>
       </c>
       <c r="H9" t="n">
-        <v>6.606760017771901</v>
+        <v>1.165567102370265</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3053682683518907</v>
+        <v>0.3052767234088358</v>
       </c>
       <c r="J9" t="n">
         <v>100</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08578757489559263</v>
+        <v>0.06785605664016992</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008749832414587756</v>
+        <v>0.005545145454472813</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -771,16 +771,16 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.037330638253033</v>
+        <v>0.03733393231122255</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04845693664255963</v>
+        <v>0.03052212432894737</v>
       </c>
       <c r="H10" t="n">
-        <v>129.8047365654742</v>
+        <v>81.75437849543763</v>
       </c>
       <c r="I10" t="n">
-        <v>0.037330638253033</v>
+        <v>0.03733393231122255</v>
       </c>
       <c r="J10" t="n">
         <v>100</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.447315604758241e-05</v>
+        <v>7.966594451123098e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>9.482588146495875e-07</v>
+        <v>8.528199987471236e-07</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -808,10 +808,10 @@
         <v>8.289751980873394e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.575636238848469e-06</v>
+        <v>3.231575297502965e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.90070371524247</v>
+        <v>3.898277421277556</v>
       </c>
       <c r="I11" t="n">
         <v>8.289751980873394e-05</v>
